--- a/backend/tests_v1/fixtures/test_equity_feb_fixture.xlsx
+++ b/backend/tests_v1/fixtures/test_equity_feb_fixture.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+  </numFmts>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -46,8 +48,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -454,10 +457,8 @@
           <t>Rent</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>03-02-2025</t>
-        </is>
+      <c r="B2" s="1" t="n">
+        <v>45691</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -481,10 +482,8 @@
           <t>Sales</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>07-02-2025</t>
-        </is>
+      <c r="B3" s="1" t="n">
+        <v>45695</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -508,10 +507,8 @@
           <t>Fee</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>10-02-2025</t>
-        </is>
+      <c r="B4" s="1" t="n">
+        <v>45698</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -523,7 +520,6 @@
           <t>55,300.00</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -531,10 +527,8 @@
           <t>Refund</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>14-02-2025</t>
-        </is>
+      <c r="B5" s="1" t="n">
+        <v>45702</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -558,10 +552,8 @@
           <t>Withdrawal</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>18-02-2025</t>
-        </is>
+      <c r="B6" s="1" t="n">
+        <v>45706</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -585,10 +577,8 @@
           <t>Top up</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>21-02-2025</t>
-        </is>
+      <c r="B7" s="1" t="n">
+        <v>45709</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -612,10 +602,8 @@
           <t>Tax</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>25-02-2025</t>
-        </is>
+      <c r="B8" s="1" t="n">
+        <v>45713</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -627,7 +615,6 @@
           <t>62,949.25</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -635,10 +622,8 @@
           <t>Closing</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>28-02-2025</t>
-        </is>
+      <c r="B9" s="1" t="n">
+        <v>45716</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
